--- a/public/samples/VoltAmpereToWatt.xlsx
+++ b/public/samples/VoltAmpereToWatt.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\programing\backend testing\dev sync for wattwizart\public\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Downloads\ezzat\WattWizards\backend\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8088D4ED-1C5E-4E68-9128-70F871C9271B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BCBFF9-7CBD-4F58-A7D9-E376E5FCD3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
     <t>Ampere</t>
   </si>
   <si>
-    <t>PowerFactor</t>
+    <t>Power factor</t>
   </si>
 </sst>
 </file>
